--- a/문서/Monster/MonsterDropData.xlsx
+++ b/문서/Monster/MonsterDropData.xlsx
@@ -1089,8 +1089,8 @@
       <c r="C2" s="1">
         <v>1001</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
+      <c r="D2" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
@@ -1115,8 +1115,8 @@
       <c r="C3" s="1">
         <v>2001</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>46</v>
+      <c r="D3" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -1141,8 +1141,8 @@
       <c r="C4" s="1">
         <v>1001</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>47</v>
+      <c r="D4" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -1167,8 +1167,8 @@
       <c r="C5" s="1">
         <v>2001</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
+      <c r="D5" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
